--- a/reports/FINRA_Open_Work.xlsx
+++ b/reports/FINRA_Open_Work.xlsx
@@ -15,11 +15,11 @@
   </sheets>
   <definedNames>
     <definedName function="false" hidden="false" localSheetId="3" name="_xlnm.Print_Titles" vbProcedure="false">'For Review'!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'For Review'!$A$4:$H$7</definedName>
+    <definedName function="false" hidden="true" localSheetId="3" name="_xlnm._FilterDatabase" vbProcedure="false">'For Review'!$A$4:$H$8</definedName>
     <definedName function="false" hidden="false" localSheetId="2" name="_xlnm.Print_Titles" vbProcedure="false">'Other FINRA'!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Other FINRA'!$A$4:$H$19</definedName>
+    <definedName function="false" hidden="true" localSheetId="2" name="_xlnm._FilterDatabase" vbProcedure="false">'Other FINRA'!$A$4:$H$133</definedName>
     <definedName function="false" hidden="false" localSheetId="1" name="_xlnm.Print_Titles" vbProcedure="false">'Prod Pod'!$4:$4</definedName>
-    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Prod Pod'!$A$4:$H$5</definedName>
+    <definedName function="false" hidden="true" localSheetId="1" name="_xlnm._FilterDatabase" vbProcedure="false">'Prod Pod'!$A$4:$H$6</definedName>
   </definedNames>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -31,12 +31,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="213" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1036" uniqueCount="480">
   <si>
     <t xml:space="preserve">FINRA — Open Work Report</t>
   </si>
   <si>
-    <t xml:space="preserve">Jira (megatron) · as of 14 Oct 2026 · In Progress, Needs Analysis</t>
+    <t xml:space="preserve">Jira (megatron) · as of 14 Oct 2026 · In Progress, Needs Analysis, To Do</t>
   </si>
   <si>
     <t xml:space="preserve">Open FINRA tickets</t>
@@ -48,6 +48,9 @@
     <t xml:space="preserve">Needs Analysis</t>
   </si>
   <si>
+    <t xml:space="preserve">To Do</t>
+  </si>
+  <si>
     <t xml:space="preserve">Prod Pod</t>
   </si>
   <si>
@@ -87,21 +90,45 @@
     <t xml:space="preserve">Bleta Jashari</t>
   </si>
   <si>
+    <t xml:space="preserve">Corinne Tighe</t>
+  </si>
+  <si>
     <t xml:space="preserve">Dalvinder Grewal</t>
   </si>
   <si>
+    <t xml:space="preserve">James Simmons</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mansi Chadha</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Milan Dusara</t>
+  </si>
+  <si>
     <t xml:space="preserve">Mitali Bhavsar</t>
   </si>
   <si>
     <t xml:space="preserve">Pavan Vemunuri</t>
   </si>
   <si>
+    <t xml:space="preserve">Prabhjot Singh</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Rohith Kunnilethu</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ryo Poc</t>
+  </si>
+  <si>
     <t xml:space="preserve">Sanchivan Sivadasan</t>
   </si>
   <si>
     <t xml:space="preserve">Satwinder Randhawa</t>
   </si>
   <si>
+    <t xml:space="preserve">Thiva Varatharajah</t>
+  </si>
+  <si>
     <t xml:space="preserve">Timothy Chiang</t>
   </si>
   <si>
@@ -111,10 +138,10 @@
     <t xml:space="preserve">How tickets were selected</t>
   </si>
   <si>
-    <t xml:space="preserve">• Current status is In Progress or Needs Analysis.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Client field = FINRA, “FINRA” or the “FIN -” project prefix in the title, or a FINRA parent ticket; titles, descriptions and comments were all searched.</t>
+    <t xml:space="preserve">• Current status is In Progress, Needs Analysis or To Do.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Client field = FINRA, “FINRA” or the “FIN -” project prefix in the title, or a FINRA / “FIN -” parent ticket; titles, descriptions and comments were all searched.</t>
   </si>
   <si>
     <t xml:space="preserve">• Prod Pod = tickets assigned to Shibi Ramaiyan or Yetunde Sanusi.</t>
@@ -123,13 +150,13 @@
     <t xml:space="preserve">• Notes flag tickets with no update in over 90 days, multi-client tickets and subtasks.</t>
   </si>
   <si>
-    <t xml:space="preserve">• The ‘For Review’ tab lists 3 ETL 2.0 pilot tickets not counted: they cover FINRA alongside Rogers and Anaplan.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Not counted: CR-489 (DEL) and MEG-33053 (Block), which only mention FINRA in passing.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">• Hours Logged is the total time logged on each ticket in Jira, all time, including child tickets (MEG-18805 and MEG-20107 hours come from their children).</t>
+    <t xml:space="preserve">• The ‘For Review’ tab lists 4 multi-client tickets not counted: 3 ETL 2.0 pilot tickets and IR-907 (reporting issue across 10 clients).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Not counted: CR-489 (DEL), MEG-33053, MEG-21407 and MEG-28712 (Block/BMO) and MEG-24951 (cancelled GBC clone), which only mention FINRA or FIN in passing.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">• Hours Logged is the total time logged on each ticket in Jira, all time, including subtasks. Epics count only their own time; child-ticket hours are in the Notes column so nothing is counted twice.</t>
   </si>
   <si>
     <t xml:space="preserve">• Last Updated is the ticket's last-updated date in Jira. Totals are live formulas over the Prod Pod and Other FINRA tabs.</t>
@@ -171,6 +198,18 @@
     <t xml:space="preserve">Multi-client: Client field = Breakthru, FINRA, Anaplan, OPS</t>
   </si>
   <si>
+    <t xml:space="preserve">IP-2856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Financial Approver Visibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Darci Frye</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-10-14</t>
+  </si>
+  <si>
     <t xml:space="preserve">Total hours logged</t>
   </si>
   <si>
@@ -234,6 +273,69 @@
     <t xml:space="preserve">No update in 518 days</t>
   </si>
   <si>
+    <t xml:space="preserve">MEG-19851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH-To Test Auto-calculate OT rates on Engagement Assignment and on Convert to Engagement</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Suman Dsa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test · Under MEG-20726 FIN-QA Testing · No update in 317 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH- To Test if Users are prevented from cloning Vendor Sourced Or Payroll, Engagement Assignments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH- To Test view/edit access of users (VMO MSP, HM and Suppliers) on Rate object on assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ASSUMPTION - Master Data Files sync'ing daily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under MEG-18947 FIN - PROD Cutover Activities · No update in 461 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To test Clone Engagement Assignment - HeadCount Assignments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To test Clone Engagement Assignment  -  Clone Assignments</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test · Under MEG-20726 FIN-QA Testing · No update in 315 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To test Create Rate and Set Rate as Primary rate.</t>
+  </si>
+  <si>
     <t xml:space="preserve">MEG-20107</t>
   </si>
   <si>
@@ -249,10 +351,10 @@
     <t xml:space="preserve">MEG-20258</t>
   </si>
   <si>
-    <t xml:space="preserve">Provision API Access to Client (FIN - Client Training &amp; Support of API)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">No update in 558 days</t>
+    <t xml:space="preserve">Provision API Access to Client</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under MEG-19265 FIN - Client Training &amp; Support of API · No update in 558 days</t>
   </si>
   <si>
     <t xml:space="preserve">MEG-20651</t>
@@ -291,7 +393,7 @@
     <t xml:space="preserve">2025-06-16</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtask of STAR-1688 FINRA Report/Dashboard prep · No update in 485 days</t>
+    <t xml:space="preserve">Under STAR-1688 FINRA Report/Dashboard prep · No update in 485 days</t>
   </si>
   <si>
     <t xml:space="preserve">STAR-1693</t>
@@ -303,7 +405,7 @@
     <t xml:space="preserve">2025-06-17</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtask of STAR-1688 FINRA Report/Dashboard prep · No update in 484 days</t>
+    <t xml:space="preserve">Under STAR-1688 FINRA Report/Dashboard prep · No update in 484 days</t>
   </si>
   <si>
     <t xml:space="preserve">STAR-1694</t>
@@ -321,7 +423,7 @@
     <t xml:space="preserve">2025-06-10</t>
   </si>
   <si>
-    <t xml:space="preserve">Subtask of STAR-1688 FINRA Report/Dashboard prep · No update in 491 days</t>
+    <t xml:space="preserve">Under STAR-1688 FINRA Report/Dashboard prep · No update in 491 days</t>
   </si>
   <si>
     <t xml:space="preserve">IP-1793</t>
@@ -330,9 +432,6 @@
     <t xml:space="preserve">FINRA - Managers receiving Approval Emails even though approval is not in their queue</t>
   </si>
   <si>
-    <t xml:space="preserve">Milan Dusara</t>
-  </si>
-  <si>
     <t xml:space="preserve">2025-10-14</t>
   </si>
   <si>
@@ -357,6 +456,975 @@
     <t xml:space="preserve">FIN - (Targeted) Regression Testing (PROD)</t>
   </si>
   <si>
+    <t xml:space="preserve">MEG-20025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To test Manual Add adjustments.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test · Under MEG-20726 FIN-QA Testing · No update in 314 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To test Clone transaction</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Auto‑Populate Offer End Date Based on Offer Start Date</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-01-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 266 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: What field is determines the locations on the integration?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-02-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 232 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">In FINRA Prod, Open Date/Time field is being overwritten when Req Assignment status is changed from Open to Draft/In Review to add new vendors and then changed to Open again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 197 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Supplier Attributes Updated to IT Preferred</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 120 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Central Notification Center (Suppliers &amp; Managers)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Delegation Visibility</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 112 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: PO dates extended via Extension Workflow</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Update Case Visibility for HM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-16</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Jake Galbrith Dashboard Creation Access</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: 1074 Approval Authority – Supervisory Organization Manager Decoupling Review</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-26</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-1421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Supplier Task and Approval Notification Enhancements</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">CR-859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Clean up redundant position fields on the assignment and redundant position records</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 378 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP-2525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Send to Workday Error Message</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-15</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 182 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP-2879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA - When they rehire, the wizard creates a duplicate contrator contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-06-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 114 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP-3022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA: Requisition Filled Email- Sending twice</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-08-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IP-3170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Birthdays in dataloaded legacy contractors have the wrong birthdays</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-09-29</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expense Report Approval Delegation – Handling End of Delegation Period (In-Flight Approvals)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 203 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-450</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA - Callout Record Analysis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 449 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA - Training to Schedule Reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 429 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Disabled Before Trigger Flow Analysis and Fix</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-09-17</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 392 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Handle outstanding assignments that need to be retriggered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Business to decide if contacts is an issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Handle outstanding cases that need to be retriggered</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Business to decide if rates is an issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Business to decide if tasks (finger printing) is an issue</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA - can we please have Inbound Integration Record in Timesheet quick links</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Katy Godfrey</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-04-10</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 187 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18880</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Business</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · No update in 596 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18920</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Configuration</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 0.5 h logged across its child tickets (not counted) · No update in 643 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - REQ Wizard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-03</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 49.75 h logged across its child tickets (not counted) · No update in 590 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Requisitions</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 37 h logged across its child tickets (not counted) · No update in 643 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Transactions / Invoicing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 18.5 h logged across its child tickets (not counted) · No update in 643 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Approvals (spend)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-31</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 95 h logged across its child tickets (not counted) · No update in 621 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Unit Sheet (VMS)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 4 h logged across its child tickets (not counted) · No update in 643 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Expense</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-24</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 66.25 h logged across its child tickets (not counted) · No update in 628 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - On Boarding / Off boarding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 48.5 h logged across its child tickets (not counted) · No update in 643 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Custom Reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Standard Reports</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-06</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under MEG-18880 FIN - Business · No update in 587 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dashboards</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Field Tracking</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Profile / User Roles</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 28 h logged across its child tickets (not counted) · No update in 590 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Submission / Candidate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 189.75 h logged across its child tickets (not counted) · No update in 593 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Engagement Management</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04-08</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 173.25 h logged across its child tickets (not counted) · No update in 554 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integration - Timesheets</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-09</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 122 h logged across its child tickets (not counted) · No update in 523 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integration - Master Data (SFTP)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 160 h logged across its child tickets (not counted) · No update in 590 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integration - New Hire / Rehire - Workday (API)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 98.0333 h logged across its child tickets (not counted) · No update in 621 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integration - Workday Financials (XML)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 40 h logged across its child tickets (not counted) · No update in 621 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - PROD Cutover Activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 0.5 h logged across its child tickets (not counted) · No update in 546 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Go-Live</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 10 h logged across its child tickets (not counted) · No update in 589 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup MSP User</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-18956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup Payroll Supplier - Account &amp; Contact</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integrations - Other</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 61 h logged across its child tickets (not counted) · No update in 596 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Setup Holiday Schedule - 2025 and 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integration Connectivity</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-01-23</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 28 h logged across its child tickets (not counted) · No update in 629 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19200</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN Regression Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test set · No update in 317 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Data Migration (load sheets)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · No update in 621 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test / UAT Load Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Under MEG-19224 FIN - Data Migration (load sheets) · No update in 621 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Production Load Sheet</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integration - Termination and Change HM (API)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-04-01</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 11 h logged across its child tickets (not counted) · No update in 561 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integration Workflow Scenarios</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 152.333 h logged across its child tickets (not counted) · No update in 593 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Email Templates / Triggers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Add Interviewer - Whenever new Interview request is created HM should be auto -added to the list of interviewers</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-08-21</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 419 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Rename MSP everywhere in email templates to VMO (FINRA terminology)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 530 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19440</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Phase 2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-02-14</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · No update in 607 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Data Migration / Load Sheets (PROD) - IT Validation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Strip off all [x] Deprecated field visibility all users</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 593 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Integration - Worker Updates - Workday (API)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-03-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 14 h logged across its child tickets (not counted) · No update in 215 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - QA/FULL Deployment &amp; Regression Activities</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 4 h logged across its child tickets (not counted) · No update in 546 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINAL position list (100% complete)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 587 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To Test Spend Approvals on Assignments- End To End (Regular + Etensions)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - All integration connections / Master Data for PROD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Client Integration Work</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · No update in 530 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-19970</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Client must schedule Timesheet 1119 and 1120 files to drop to QA SFTP</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Setup Dev Environment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-03-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 5 h logged across its child tickets (not counted) · No update in 573 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Client to execute / plan for go-live migration (Fieldglass ID's - WK and WO)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20230</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal - To test Cancel Req- Category Screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal -To test Cancel Req -Assignment Screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal- To test Cancel Req -Position Screen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal -To test if Closing Date/time is added to a Requisition with status "Draft"/"In Review" then Requisition status is updated based on inputted Closing Date/time.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-12-02</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test · Under MEG-20726 FIN-QA Testing · No update in 316 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal -To test if Closing Date/time is added to a Requisition with status "Open"  then Requisition status is updated based on inputted Closing Date/time .</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal - To test if Vendor is unable to Create/Submit a Candidate Record when Requisition status is Evaluation, Filled, On Hold or Cancelled</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal - To Test if Vendor is able to withdraw a Candidate and then resubmit the candidate.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal - To test if Vendor is able to deny an interview request-Place holder</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal- To Test validation error message for Req Interview and Make Offer (HM) Button</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal - To test if Partial Match is applied when supplier is accepting an offer for a Candidate such that the Candidate's  Email ID matches with Existing Contractor Email ID and Candidate ID doesnot match with existing Contractor's Candidate ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20240</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Internal - To test if Partial Match is applied when supplier is accepting an offer for a Candidate such that the Candidate's Email ID  doesnot match with Existing Contractor Email ID and Candidate ID matches with existing Contractor's Candidate ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA Dev/QA Test Cycle1 April 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test execution · No update in 317 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">To test Approval Delegations</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN-QA Testing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · No update in 317 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH - FIN - To test Assignment Expiry Email Notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test · No update in 317 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">PH - FIN - To test PO Depletion Email notifications</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test · No update in 314 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-20945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - SIT Issues</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Epic · 23.5167 h logged across its child tickets (not counted) · No update in 518 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-21328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Change Request - Invoice Automation</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-05-30</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 502 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-21782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Sample-FINRA Critical and High Risk Test Scenarios Set)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test set · No update in 484 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-21937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Sample)-FIN-Placeholder Test Plan- Short Term</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test plan · No update in 317 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-21938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">(Sample-FIN-Placeholder Test Execution- Short Term)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA sub test execution · No update in 317 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-21939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN -Placeholder Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-13</t>
+  </si>
+  <si>
+    <t xml:space="preserve">QA test · No update in 488 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-21979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Test Cycle - Training June 2025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-22118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA - Bill Rate not exposed to supplier</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-19</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 482 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-22141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN-SOW/Headcount Eng-A-New fields are showing on Eng-Assignment</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-07-11</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 460 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-22234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN - Workday Production Connectivity Test</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-06-25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 476 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-22495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN- Refresh full? Discuss</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2025-10-28</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 351 days</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MEG-22540</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FIN-Eng-Assignment- MSP should be allowed to close all tasks</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAR-1689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Functional standard reports and dashboards library with all necessary custom reporting fields</t>
+  </si>
+  <si>
+    <t xml:space="preserve">STAR-1696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">FINRA specific reporting</t>
+  </si>
+  <si>
+    <t xml:space="preserve">No update in 491 days</t>
+  </si>
+  <si>
     <t xml:space="preserve">For Review — Not Counted in Totals</t>
   </si>
   <si>
@@ -391,6 +1459,18 @@
   </si>
   <si>
     <t xml:space="preserve">Multi-client ETL 2.0 pilot: workloads include FINRA 400 and Rogers 1500</t>
+  </si>
+  <si>
+    <t xml:space="preserve">IR-907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify Your Identity Prompt When Exporting Reports - Wrong Report Output than Selected</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026-07-22</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Multi-client: FINRA is one of 10 clients affected (with Anaplan, Deloitte, FanDuel, KPMG, PwC and others)</t>
   </si>
 </sst>
 </file>
@@ -404,7 +1484,7 @@
     <numFmt numFmtId="167" formatCode="0.00&quot; h&quot;"/>
     <numFmt numFmtId="168" formatCode="0.00&quot; h&quot;;;&quot;0 h&quot;"/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -469,6 +1549,14 @@
       <b val="true"/>
       <sz val="22"/>
       <color rgb="FFD97706"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="22"/>
+      <color rgb="FF475569"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -544,6 +1632,14 @@
     <font>
       <sz val="10"/>
       <color rgb="FF64748B"/>
+      <name val="Arial"/>
+      <family val="0"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="10"/>
+      <color rgb="FF475569"/>
       <name val="Arial"/>
       <family val="0"/>
       <charset val="1"/>
@@ -655,14 +1751,14 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF2B59C3"/>
-        <bgColor rgb="FF2563EB"/>
+        <fgColor rgb="FFF8FAFC"/>
+        <bgColor rgb="FFFFFFFF"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF8FAFC"/>
-        <bgColor rgb="FFFFFFFF"/>
+        <fgColor rgb="FF2B59C3"/>
+        <bgColor rgb="FF2563EB"/>
       </patternFill>
     </fill>
     <fill>
@@ -724,7 +1820,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="52">
+  <cellXfs count="56">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -757,47 +1853,47 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="166" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="11" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="166" fontId="12" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="165" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -805,19 +1901,27 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="15" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="16" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -829,43 +1933,67 @@
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="13" fillId="2" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="17" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="18" fillId="5" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="17" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="26" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="27" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="27" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="21" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="168" fontId="16" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -873,55 +2001,39 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="167" fontId="20" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="167" fontId="22" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="5" fillId="7" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="8" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="1" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="14" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="28" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="168" fontId="15" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="168" fontId="16" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="168" fontId="28" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="29" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="26" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="27" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="168" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="28" fillId="8" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="30" fillId="7" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -942,11 +2054,19 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="12">
+  <dxfs count="14">
     <dxf>
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FF14213D"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FFF8FAFC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -977,7 +2097,23 @@
     <dxf>
       <fill>
         <patternFill patternType="solid">
+          <fgColor rgb="FFF1F5F9"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
           <fgColor rgb="FFFEF3C7"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF475569"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1010,14 +2146,6 @@
       <fill>
         <patternFill patternType="solid">
           <fgColor rgb="FFB45309"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FFF8FAFC"/>
           <bgColor rgb="FF000000"/>
         </patternFill>
       </fill>
@@ -1200,28 +2328,34 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$A$9:$A$10</c:f>
+              <c:f>Summary!$A$9:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>In Progress</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Needs Analysis</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>To Do</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$B$9:$B$10</c:f>
+              <c:f>Summary!$B$9:$B$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
                 <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
                   <c:v>1</c:v>
                 </c:pt>
               </c:numCache>
@@ -1281,29 +2415,35 @@
           </c:dLbls>
           <c:cat>
             <c:strRef>
-              <c:f>Summary!$A$9:$A$10</c:f>
+              <c:f>Summary!$A$9:$A$11</c:f>
               <c:strCache>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
                   <c:v>In Progress</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>Needs Analysis</c:v>
                 </c:pt>
+                <c:pt idx="2">
+                  <c:v>To Do</c:v>
+                </c:pt>
               </c:strCache>
             </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Summary!$C$9:$C$10</c:f>
+              <c:f>Summary!$C$9:$C$11</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="2"/>
+                <c:ptCount val="3"/>
                 <c:pt idx="0">
-                  <c:v>12</c:v>
+                  <c:v>19</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>3</c:v>
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>105</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1311,11 +2451,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="100"/>
-        <c:axId val="29041258"/>
-        <c:axId val="74207014"/>
+        <c:axId val="96067594"/>
+        <c:axId val="93176433"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="29041258"/>
+        <c:axId val="96067594"/>
         <c:scaling>
           <c:orientation val="maxMin"/>
         </c:scaling>
@@ -1347,7 +2487,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74207014"/>
+        <c:crossAx val="93176433"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -1355,7 +2495,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="74207014"/>
+        <c:axId val="93176433"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -1421,7 +2561,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="29041258"/>
+        <c:crossAx val="96067594"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -1479,13 +2619,13 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>19</xdr:row>
+      <xdr:row>27</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>5</xdr:col>
       <xdr:colOff>1115280</xdr:colOff>
-      <xdr:row>33</xdr:row>
+      <xdr:row>41</xdr:row>
       <xdr:rowOff>32760</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame>
@@ -1494,7 +2634,7 @@
         <xdr:cNvGraphicFramePr/>
       </xdr:nvGraphicFramePr>
       <xdr:xfrm>
-        <a:off x="0" y="4086360"/>
+        <a:off x="0" y="5610240"/>
         <a:ext cx="6119640" cy="2699640"/>
       </xdr:xfrm>
       <a:graphic>
@@ -1701,7 +2841,7 @@
     <tabColor rgb="FF14213D"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:I44"/>
+  <dimension ref="A1:I52"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="26"/>
@@ -1754,303 +2894,453 @@
       <c r="F4" s="3" t="s">
         <v>6</v>
       </c>
+      <c r="G4" s="3" t="s">
+        <v>7</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="33.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="4" t="n">
-        <f aca="false">COUNTA('Prod Pod'!$C$5:$C$5)+COUNTA('Other FINRA'!$C$5:$C$19)</f>
+        <f aca="false">COUNTA('Prod Pod'!$C$5:$C$6)+COUNTA('Other FINRA'!$C$5:$C$133)</f>
+        <v>131</v>
+      </c>
+      <c r="B5" s="5" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$6,"In Progress")+COUNTIF('Other FINRA'!$C$5:$C$133,"In Progress")</f>
+        <v>19</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$6,"Needs Analysis")+COUNTIF('Other FINRA'!$C$5:$C$133,"Needs Analysis")</f>
+        <v>6</v>
+      </c>
+      <c r="D5" s="7" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$6,"To Do")+COUNTIF('Other FINRA'!$C$5:$C$133,"To Do")</f>
+        <v>106</v>
+      </c>
+      <c r="F5" s="8" t="n">
+        <f aca="false">COUNTA('Prod Pod'!$C$5:$C$6)</f>
+        <v>2</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <f aca="false">SUM('Prod Pod'!$G$5:$G$6)+SUM('Other FINRA'!$G$5:$G$133)</f>
+        <v>52</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="10" t="s">
+        <v>8</v>
+      </c>
+      <c r="B8" s="11" t="s">
+        <v>6</v>
+      </c>
+      <c r="C8" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="D8" s="11" t="s">
+        <v>10</v>
+      </c>
+      <c r="F8" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="G8" s="12" t="s">
+        <v>12</v>
+      </c>
+      <c r="H8" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="I8" s="12" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="13" t="s">
+        <v>3</v>
+      </c>
+      <c r="B9" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$6,A9)</f>
+        <v>0</v>
+      </c>
+      <c r="C9" s="14" t="n">
+        <f aca="false">COUNTIF('Other FINRA'!$C$5:$C$133,A9)</f>
+        <v>19</v>
+      </c>
+      <c r="D9" s="15" t="n">
+        <f aca="false">B9+C9</f>
+        <v>19</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>15</v>
+      </c>
+      <c r="G9" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F9)+COUNTIF('Other FINRA'!$E$5:$E$133,F9)</f>
+        <v>2</v>
+      </c>
+      <c r="H9" s="16" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F9,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F9,'Other FINRA'!$G$5:$G$133)</f>
+        <v>4</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="18" t="s">
+        <v>4</v>
+      </c>
+      <c r="B10" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$6,A10)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="14" t="n">
+        <f aca="false">COUNTIF('Other FINRA'!$C$5:$C$133,A10)</f>
+        <v>5</v>
+      </c>
+      <c r="D10" s="15" t="n">
+        <f aca="false">B10+C10</f>
+        <v>6</v>
+      </c>
+      <c r="F10" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="5" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$5,"In Progress")+COUNTIF('Other FINRA'!$C$5:$C$19,"In Progress")</f>
-        <v>12</v>
-      </c>
-      <c r="C5" s="6" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$5,"Needs Analysis")+COUNTIF('Other FINRA'!$C$5:$C$19,"Needs Analysis")</f>
-        <v>4</v>
-      </c>
-      <c r="D5" s="7" t="n">
-        <f aca="false">COUNTA('Prod Pod'!$C$5:$C$5)</f>
+      <c r="G10" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F10)+COUNTIF('Other FINRA'!$E$5:$E$133,F10)</f>
         <v>1</v>
       </c>
-      <c r="F5" s="8" t="n">
-        <f aca="false">SUM('Prod Pod'!$G$5:$G$5)+SUM('Other FINRA'!$G$5:$G$19)</f>
+      <c r="H10" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I10" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F10,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F10,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="21" t="s">
+        <v>5</v>
+      </c>
+      <c r="B11" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$6,A11)</f>
+        <v>1</v>
+      </c>
+      <c r="C11" s="14" t="n">
+        <f aca="false">COUNTIF('Other FINRA'!$C$5:$C$133,A11)</f>
+        <v>105</v>
+      </c>
+      <c r="D11" s="15" t="n">
+        <f aca="false">B11+C11</f>
+        <v>106</v>
+      </c>
+      <c r="F11" s="19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F11)+COUNTIF('Other FINRA'!$E$5:$E$133,F11)</f>
+        <v>8</v>
+      </c>
+      <c r="H11" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I11" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F11,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F11,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="22" t="s">
+        <v>10</v>
+      </c>
+      <c r="B12" s="23" t="n">
+        <f aca="false">SUM(B9:B11)</f>
+        <v>2</v>
+      </c>
+      <c r="C12" s="23" t="n">
+        <f aca="false">SUM(C9:C11)</f>
+        <v>129</v>
+      </c>
+      <c r="D12" s="23" t="n">
+        <f aca="false">SUM(D9:D11)</f>
+        <v>131</v>
+      </c>
+      <c r="F12" s="19" t="s">
+        <v>19</v>
+      </c>
+      <c r="G12" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F12)+COUNTIF('Other FINRA'!$E$5:$E$133,F12)</f>
+        <v>1</v>
+      </c>
+      <c r="H12" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I12" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F12,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F12,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F13" s="19" t="s">
+        <v>20</v>
+      </c>
+      <c r="G13" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F13)+COUNTIF('Other FINRA'!$E$5:$E$133,F13)</f>
+        <v>1</v>
+      </c>
+      <c r="H13" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I13" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F13,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F13,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F14" s="19" t="s">
+        <v>21</v>
+      </c>
+      <c r="G14" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F14)+COUNTIF('Other FINRA'!$E$5:$E$133,F14)</f>
+        <v>8</v>
+      </c>
+      <c r="H14" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I14" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F14,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F14,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F15" s="19" t="s">
+        <v>22</v>
+      </c>
+      <c r="G15" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F15)+COUNTIF('Other FINRA'!$E$5:$E$133,F15)</f>
+        <v>1</v>
+      </c>
+      <c r="H15" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I15" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F15,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F15,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F16" s="19" t="s">
+        <v>23</v>
+      </c>
+      <c r="G16" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F16)+COUNTIF('Other FINRA'!$E$5:$E$133,F16)</f>
+        <v>1</v>
+      </c>
+      <c r="H16" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I16" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F16,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F16,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F17" s="19" t="s">
+        <v>24</v>
+      </c>
+      <c r="G17" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F17)+COUNTIF('Other FINRA'!$E$5:$E$133,F17)</f>
+        <v>3</v>
+      </c>
+      <c r="H17" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I17" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F17,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F17,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F18" s="19" t="s">
+        <v>25</v>
+      </c>
+      <c r="G18" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F18)+COUNTIF('Other FINRA'!$E$5:$E$133,F18)</f>
+        <v>1</v>
+      </c>
+      <c r="H18" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I18" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F18,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F18,'Other FINRA'!$G$5:$G$133)</f>
+        <v>21</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F19" s="19" t="s">
+        <v>26</v>
+      </c>
+      <c r="G19" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F19)+COUNTIF('Other FINRA'!$E$5:$E$133,F19)</f>
+        <v>1</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I19" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F19,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F19,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F20" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="G20" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F20)+COUNTIF('Other FINRA'!$E$5:$E$133,F20)</f>
+        <v>1</v>
+      </c>
+      <c r="H20" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I20" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F20,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F20,'Other FINRA'!$G$5:$G$133)</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F21" s="19" t="s">
+        <v>28</v>
+      </c>
+      <c r="G21" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F21)+COUNTIF('Other FINRA'!$E$5:$E$133,F21)</f>
+        <v>2</v>
+      </c>
+      <c r="H21" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I21" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F21,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F21,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F22" s="19" t="s">
+        <v>29</v>
+      </c>
+      <c r="G22" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F22)+COUNTIF('Other FINRA'!$E$5:$E$133,F22)</f>
+        <v>1</v>
+      </c>
+      <c r="H22" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I22" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F22,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F22,'Other FINRA'!$G$5:$G$133)</f>
+        <v>5</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F23" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="G23" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F23)+COUNTIF('Other FINRA'!$E$5:$E$133,F23)</f>
+        <v>5</v>
+      </c>
+      <c r="H23" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I23" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F23,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F23,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F24" s="19" t="s">
+        <v>31</v>
+      </c>
+      <c r="G24" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F24)+COUNTIF('Other FINRA'!$E$5:$E$133,F24)</f>
+        <v>1</v>
+      </c>
+      <c r="H24" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I24" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F24,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F24,'Other FINRA'!$G$5:$G$133)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F25" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="G25" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,F25)+COUNTIF('Other FINRA'!$E$5:$E$133,F25)</f>
+        <v>2</v>
+      </c>
+      <c r="H25" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I25" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F25,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F25,'Other FINRA'!$G$5:$G$133)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="F26" s="19" t="s">
+        <v>33</v>
+      </c>
+      <c r="G26" s="14" t="n">
+        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$6,"Unassigned")+COUNTIF('Other FINRA'!$E$5:$E$133,"Unassigned")</f>
+        <v>91</v>
+      </c>
+      <c r="H26" s="20" t="s">
+        <v>17</v>
+      </c>
+      <c r="I26" s="17" t="n">
+        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$6,F26,'Prod Pod'!$G$5:$G$6)+SUMIF('Other FINRA'!$E$5:$E$133,F26,'Other FINRA'!$G$5:$G$133)</f>
+        <v>13</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="24" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="25" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="25" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="25" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="25" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="25" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B8" s="10" t="s">
-        <v>5</v>
-      </c>
-      <c r="C8" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>9</v>
-      </c>
-      <c r="F8" s="11" t="s">
-        <v>10</v>
-      </c>
-      <c r="G8" s="11" t="s">
-        <v>11</v>
-      </c>
-      <c r="H8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="I8" s="11" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="12" t="s">
-        <v>3</v>
-      </c>
-      <c r="B9" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$5,A9)</f>
-        <v>0</v>
-      </c>
-      <c r="C9" s="13" t="n">
-        <f aca="false">COUNTIF('Other FINRA'!$C$5:$C$19,A9)</f>
-        <v>12</v>
-      </c>
-      <c r="D9" s="14" t="n">
-        <f aca="false">B9+C9</f>
-        <v>12</v>
-      </c>
-      <c r="F9" s="15" t="s">
-        <v>14</v>
-      </c>
-      <c r="G9" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F9)+COUNTIF('Other FINRA'!$E$5:$E$19,F9)</f>
-        <v>1</v>
-      </c>
-      <c r="H9" s="15" t="s">
-        <v>5</v>
-      </c>
-      <c r="I9" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F9,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F9,'Other FINRA'!$G$5:$G$19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>4</v>
-      </c>
-      <c r="B10" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$C$5:$C$5,A10)</f>
-        <v>1</v>
-      </c>
-      <c r="C10" s="13" t="n">
-        <f aca="false">COUNTIF('Other FINRA'!$C$5:$C$19,A10)</f>
-        <v>3</v>
-      </c>
-      <c r="D10" s="14" t="n">
-        <f aca="false">B10+C10</f>
-        <v>4</v>
-      </c>
-      <c r="F10" s="18" t="s">
-        <v>15</v>
-      </c>
-      <c r="G10" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F10)+COUNTIF('Other FINRA'!$E$5:$E$19,F10)</f>
-        <v>1</v>
-      </c>
-      <c r="H10" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I10" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F10,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F10,'Other FINRA'!$G$5:$G$19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="20" t="s">
-        <v>9</v>
-      </c>
-      <c r="B11" s="21" t="n">
-        <f aca="false">SUM(B9:B10)</f>
-        <v>1</v>
-      </c>
-      <c r="C11" s="21" t="n">
-        <f aca="false">SUM(C9:C10)</f>
-        <v>15</v>
-      </c>
-      <c r="D11" s="21" t="n">
-        <f aca="false">SUM(D9:D10)</f>
-        <v>16</v>
-      </c>
-      <c r="F11" s="18" t="s">
-        <v>17</v>
-      </c>
-      <c r="G11" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F11)+COUNTIF('Other FINRA'!$E$5:$E$19,F11)</f>
-        <v>1</v>
-      </c>
-      <c r="H11" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I11" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F11,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F11,'Other FINRA'!$G$5:$G$19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F12" s="18" t="s">
-        <v>18</v>
-      </c>
-      <c r="G12" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F12)+COUNTIF('Other FINRA'!$E$5:$E$19,F12)</f>
-        <v>1</v>
-      </c>
-      <c r="H12" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I12" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F12,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F12,'Other FINRA'!$G$5:$G$19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F13" s="18" t="s">
-        <v>19</v>
-      </c>
-      <c r="G13" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F13)+COUNTIF('Other FINRA'!$E$5:$E$19,F13)</f>
-        <v>2</v>
-      </c>
-      <c r="H13" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I13" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F13,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F13,'Other FINRA'!$G$5:$G$19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F14" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G14" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F14)+COUNTIF('Other FINRA'!$E$5:$E$19,F14)</f>
-        <v>1</v>
-      </c>
-      <c r="H14" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I14" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F14,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F14,'Other FINRA'!$G$5:$G$19)</f>
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F15" s="18" t="s">
-        <v>21</v>
-      </c>
-      <c r="G15" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F15)+COUNTIF('Other FINRA'!$E$5:$E$19,F15)</f>
-        <v>1</v>
-      </c>
-      <c r="H15" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I15" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F15,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F15,'Other FINRA'!$G$5:$G$19)</f>
-        <v>5</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F16" s="18" t="s">
-        <v>22</v>
-      </c>
-      <c r="G16" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F16)+COUNTIF('Other FINRA'!$E$5:$E$19,F16)</f>
-        <v>5</v>
-      </c>
-      <c r="H16" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I16" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F16,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F16,'Other FINRA'!$G$5:$G$19)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F17" s="18" t="s">
-        <v>23</v>
-      </c>
-      <c r="G17" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,F17)+COUNTIF('Other FINRA'!$E$5:$E$19,F17)</f>
-        <v>1</v>
-      </c>
-      <c r="H17" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I17" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F17,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F17,'Other FINRA'!$G$5:$G$19)</f>
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="F18" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="G18" s="13" t="n">
-        <f aca="false">COUNTIF('Prod Pod'!$E$5:$E$5,"Unassigned")+COUNTIF('Other FINRA'!$E$5:$E$19,"Unassigned")</f>
-        <v>2</v>
-      </c>
-      <c r="H18" s="19" t="s">
-        <v>16</v>
-      </c>
-      <c r="I18" s="16" t="n">
-        <f aca="false">SUMIF('Prod Pod'!$E$5:$E$5,F18,'Prod Pod'!$G$5:$G$5)+SUMIF('Other FINRA'!$E$5:$E$19,F18,'Other FINRA'!$G$5:$G$19)</f>
-        <v>13</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="22" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="23" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A38" s="23" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A39" s="23" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="23" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A41" s="23" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="23" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="23" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="23" t="s">
-        <v>33</v>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="25" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="25" t="s">
+        <v>42</v>
       </c>
     </row>
   </sheetData>
@@ -2075,7 +3365,7 @@
     <tabColor rgb="FF0F766E"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:H7"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -2087,104 +3377,129 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="B1" s="24"/>
-      <c r="C1" s="24"/>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
+      <c r="A1" s="26" t="s">
+        <v>43</v>
+      </c>
+      <c r="B1" s="26"/>
+      <c r="C1" s="26"/>
+      <c r="D1" s="26"/>
+      <c r="E1" s="26"/>
+      <c r="F1" s="26"/>
+      <c r="G1" s="26"/>
+      <c r="H1" s="26"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="25" t="s">
-        <v>35</v>
-      </c>
-      <c r="B2" s="25"/>
-      <c r="C2" s="25"/>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
+      <c r="A2" s="27" t="s">
+        <v>44</v>
+      </c>
+      <c r="B2" s="27"/>
+      <c r="C2" s="27"/>
+      <c r="D2" s="27"/>
+      <c r="E2" s="27"/>
+      <c r="F2" s="27"/>
+      <c r="G2" s="27"/>
+      <c r="H2" s="27"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="27" t="s">
-        <v>41</v>
+      <c r="A4" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>42</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>43</v>
-      </c>
-      <c r="C5" s="30" t="s">
+      <c r="A5" s="30" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="32" t="s">
         <v>4</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>14</v>
-      </c>
-      <c r="E5" s="32" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>45</v>
+      <c r="D5" s="33" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>54</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B6" s="36"/>
-      <c r="C6" s="36"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="36"/>
-      <c r="F6" s="36"/>
-      <c r="G6" s="37" t="n">
-        <f aca="false">SUM(G5:G5)</f>
-        <v>0</v>
-      </c>
-      <c r="H6" s="36"/>
+      <c r="A6" s="37" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>58</v>
+      </c>
+      <c r="G6" s="42" t="n">
+        <v>4</v>
+      </c>
+      <c r="H6" s="38"/>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B7" s="44"/>
+      <c r="C7" s="44"/>
+      <c r="D7" s="44"/>
+      <c r="E7" s="44"/>
+      <c r="F7" s="44"/>
+      <c r="G7" s="45" t="n">
+        <f aca="false">SUM(G5:G6)</f>
+        <v>4</v>
+      </c>
+      <c r="H7" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H5"/>
+  <autoFilter ref="A4:H6"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="A5" r:id="rId1" display="IP-3012"/>
+    <hyperlink ref="A6" r:id="rId2" display="IP-2856"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2193,7 +3508,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>
 
@@ -2203,7 +3518,7 @@
     <tabColor rgb="FF2B59C3"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H20"/>
+  <dimension ref="A1:H134"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -2215,462 +3530,3414 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="38" t="s">
+      <c r="A1" s="46" t="s">
+        <v>60</v>
+      </c>
+      <c r="B1" s="46"/>
+      <c r="C1" s="46"/>
+      <c r="D1" s="46"/>
+      <c r="E1" s="46"/>
+      <c r="F1" s="46"/>
+      <c r="G1" s="46"/>
+      <c r="H1" s="46"/>
+    </row>
+    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="B2" s="47"/>
+      <c r="C2" s="47"/>
+      <c r="D2" s="47"/>
+      <c r="E2" s="47"/>
+      <c r="F2" s="47"/>
+      <c r="G2" s="47"/>
+      <c r="H2" s="47"/>
+    </row>
+    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A4" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="29" t="s">
         <v>47</v>
       </c>
-      <c r="B1" s="38"/>
-      <c r="C1" s="38"/>
-      <c r="D1" s="38"/>
-      <c r="E1" s="38"/>
-      <c r="F1" s="38"/>
-      <c r="G1" s="38"/>
-      <c r="H1" s="38"/>
-    </row>
-    <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="39" t="s">
+      <c r="E4" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="29" t="s">
         <v>48</v>
       </c>
-      <c r="B2" s="39"/>
-      <c r="C2" s="39"/>
-      <c r="D2" s="39"/>
-      <c r="E2" s="39"/>
-      <c r="F2" s="39"/>
-      <c r="G2" s="39"/>
-      <c r="H2" s="39"/>
-    </row>
-    <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="27" t="s">
-        <v>41</v>
+      <c r="G4" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="C5" s="40" t="s">
+      <c r="A5" s="30" t="s">
+        <v>62</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="C5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E5" s="41" t="s">
+      <c r="D5" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E5" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>65</v>
+      </c>
+      <c r="G5" s="50" t="n">
+        <v>13</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>68</v>
+      </c>
+      <c r="C6" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>70</v>
+      </c>
+      <c r="G6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="30" t="s">
+        <v>72</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D7" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>20</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>74</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>77</v>
+      </c>
+      <c r="C8" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E8" s="40" t="s">
         <v>24</v>
       </c>
-      <c r="F5" s="31" t="s">
-        <v>52</v>
-      </c>
-      <c r="G5" s="42" t="n">
-        <v>13</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>55</v>
-      </c>
-      <c r="C6" s="40" t="s">
+      <c r="F8" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="G8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="30" t="s">
+        <v>80</v>
+      </c>
+      <c r="B9" s="31" t="s">
+        <v>81</v>
+      </c>
+      <c r="C9" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" s="45" t="s">
+      <c r="D9" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E9" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F9" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G9" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="B10" s="38" t="s">
+        <v>86</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D10" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="E10" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G10" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="30" t="s">
+        <v>87</v>
+      </c>
+      <c r="B11" s="31" t="s">
+        <v>88</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E11" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F11" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G11" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A12" s="37" t="s">
+        <v>89</v>
+      </c>
+      <c r="B12" s="38" t="s">
+        <v>90</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D12" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E12" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F12" s="40" t="s">
+        <v>91</v>
+      </c>
+      <c r="G12" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="52" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A13" s="30" t="s">
+        <v>93</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>94</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D13" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E13" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F13" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G13" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A14" s="37" t="s">
+        <v>95</v>
+      </c>
+      <c r="B14" s="38" t="s">
+        <v>96</v>
+      </c>
+      <c r="C14" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D14" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E14" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F14" s="40" t="s">
+        <v>97</v>
+      </c>
+      <c r="G14" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="52" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A15" s="30" t="s">
+        <v>99</v>
+      </c>
+      <c r="B15" s="31" t="s">
+        <v>100</v>
+      </c>
+      <c r="C15" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D15" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E15" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F15" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G15" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A16" s="37" t="s">
+        <v>101</v>
+      </c>
+      <c r="B16" s="38" t="s">
+        <v>102</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D16" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="E16" s="40" t="s">
+        <v>25</v>
+      </c>
+      <c r="F16" s="40" t="s">
+        <v>103</v>
+      </c>
+      <c r="G16" s="42" t="n">
+        <v>21</v>
+      </c>
+      <c r="H16" s="52" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A17" s="30" t="s">
+        <v>105</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D17" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E17" s="33" t="s">
+        <v>29</v>
+      </c>
+      <c r="F17" s="33" t="s">
+        <v>103</v>
+      </c>
+      <c r="G17" s="50" t="n">
+        <v>5</v>
+      </c>
+      <c r="H17" s="36" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A18" s="37" t="s">
+        <v>108</v>
+      </c>
+      <c r="B18" s="38" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D18" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E18" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="F18" s="40" t="s">
+        <v>110</v>
+      </c>
+      <c r="G18" s="42" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" s="52" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A19" s="30" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D19" s="33" t="s">
+        <v>114</v>
+      </c>
+      <c r="E19" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F19" s="33" t="s">
+        <v>115</v>
+      </c>
+      <c r="G19" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="36" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A20" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="B20" s="38" t="s">
+        <v>118</v>
+      </c>
+      <c r="C20" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D20" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E20" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="F20" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="G20" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A21" s="30" t="s">
+        <v>121</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C21" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E21" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F21" s="33" t="s">
+        <v>123</v>
+      </c>
+      <c r="G21" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="36" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A22" s="37" t="s">
+        <v>125</v>
+      </c>
+      <c r="B22" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="C22" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D22" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E22" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="F22" s="40" t="s">
+        <v>119</v>
+      </c>
+      <c r="G22" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="52" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A23" s="30" t="s">
+        <v>127</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>128</v>
+      </c>
+      <c r="C23" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="D23" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E23" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="F23" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="G23" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="36" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A24" s="37" t="s">
+        <v>131</v>
+      </c>
+      <c r="B24" s="38" t="s">
+        <v>132</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D24" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E24" s="40" t="s">
+        <v>16</v>
+      </c>
+      <c r="F24" s="40" t="s">
+        <v>133</v>
+      </c>
+      <c r="G24" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="52" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A25" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D25" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E25" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F25" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="G25" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="36" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A26" s="37" t="s">
+        <v>139</v>
+      </c>
+      <c r="B26" s="38" t="s">
+        <v>140</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D26" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E26" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F26" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="G26" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="52" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A27" s="30" t="s">
+        <v>141</v>
+      </c>
+      <c r="B27" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D27" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E27" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F27" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="G27" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="36" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A28" s="37" t="s">
+        <v>145</v>
+      </c>
+      <c r="B28" s="38" t="s">
+        <v>146</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>4</v>
+      </c>
+      <c r="D28" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E28" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F28" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G28" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A29" s="30" t="s">
+        <v>147</v>
+      </c>
+      <c r="B29" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="C29" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="33" t="s">
         <v>57</v>
       </c>
-      <c r="G6" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="47" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
+      <c r="E29" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F29" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="G29" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" s="36" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A30" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="B30" s="38" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F30" s="40" t="s">
+        <v>153</v>
+      </c>
+      <c r="G30" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A31" s="30" t="s">
+        <v>155</v>
+      </c>
+      <c r="B31" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E31" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F31" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="G31" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="36" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A32" s="37" t="s">
+        <v>159</v>
+      </c>
+      <c r="B32" s="38" t="s">
+        <v>160</v>
+      </c>
+      <c r="C32" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F32" s="40" t="s">
+        <v>161</v>
+      </c>
+      <c r="G32" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="52" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A33" s="30" t="s">
+        <v>163</v>
+      </c>
+      <c r="B33" s="31" t="s">
+        <v>164</v>
+      </c>
+      <c r="C33" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E33" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F33" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="36" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A34" s="37" t="s">
+        <v>165</v>
+      </c>
+      <c r="B34" s="38" t="s">
+        <v>166</v>
+      </c>
+      <c r="C34" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F34" s="40" t="s">
+        <v>167</v>
+      </c>
+      <c r="G34" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" s="52" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A35" s="30" t="s">
+        <v>169</v>
+      </c>
+      <c r="B35" s="31" t="s">
+        <v>170</v>
+      </c>
+      <c r="C35" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E35" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F35" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="G35" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="36" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A36" s="37" t="s">
+        <v>171</v>
+      </c>
+      <c r="B36" s="38" t="s">
+        <v>172</v>
+      </c>
+      <c r="C36" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F36" s="40" t="s">
+        <v>173</v>
+      </c>
+      <c r="G36" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="38"/>
+    </row>
+    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A37" s="30" t="s">
+        <v>174</v>
+      </c>
+      <c r="B37" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="C37" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E37" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F37" s="33" t="s">
+        <v>176</v>
+      </c>
+      <c r="G37" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="31"/>
+    </row>
+    <row r="38" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A38" s="37" t="s">
+        <v>177</v>
+      </c>
+      <c r="B38" s="38" t="s">
+        <v>178</v>
+      </c>
+      <c r="C38" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F38" s="40" t="s">
+        <v>179</v>
+      </c>
+      <c r="G38" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="38"/>
+    </row>
+    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A39" s="30" t="s">
+        <v>180</v>
+      </c>
+      <c r="B39" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C39" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E39" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F39" s="33" t="s">
+        <v>182</v>
+      </c>
+      <c r="G39" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="31"/>
+    </row>
+    <row r="40" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A40" s="37" t="s">
+        <v>183</v>
+      </c>
+      <c r="B40" s="38" t="s">
+        <v>184</v>
+      </c>
+      <c r="C40" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F40" s="40" t="s">
+        <v>185</v>
+      </c>
+      <c r="G40" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="52" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A41" s="30" t="s">
+        <v>187</v>
+      </c>
+      <c r="B41" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C41" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E41" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F41" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="G41" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="36" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A42" s="37" t="s">
+        <v>191</v>
+      </c>
+      <c r="B42" s="38" t="s">
+        <v>192</v>
+      </c>
+      <c r="C42" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E42" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="F42" s="40" t="s">
+        <v>193</v>
+      </c>
+      <c r="G42" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="52" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A43" s="30" t="s">
+        <v>195</v>
+      </c>
+      <c r="B43" s="31" t="s">
+        <v>196</v>
+      </c>
+      <c r="C43" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="33" t="s">
+        <v>57</v>
+      </c>
+      <c r="E43" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F43" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="G43" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="31"/>
+    </row>
+    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A44" s="37" t="s">
+        <v>198</v>
+      </c>
+      <c r="B44" s="38" t="s">
+        <v>199</v>
+      </c>
+      <c r="C44" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E44" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F44" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="G44" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="38"/>
+    </row>
+    <row r="45" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="30" t="s">
+        <v>201</v>
+      </c>
+      <c r="B45" s="31" t="s">
+        <v>202</v>
+      </c>
+      <c r="C45" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E45" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F45" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G45" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="37" t="s">
+        <v>205</v>
+      </c>
+      <c r="B46" s="38" t="s">
+        <v>206</v>
+      </c>
+      <c r="C46" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="40" t="s">
+        <v>23</v>
+      </c>
+      <c r="E46" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F46" s="40" t="s">
+        <v>207</v>
+      </c>
+      <c r="G46" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H46" s="52" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A47" s="30" t="s">
+        <v>209</v>
+      </c>
+      <c r="B47" s="31" t="s">
+        <v>210</v>
+      </c>
+      <c r="C47" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="33" t="s">
+        <v>23</v>
+      </c>
+      <c r="E47" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="F47" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="G47" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="36" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="37" t="s">
+        <v>213</v>
+      </c>
+      <c r="B48" s="38" t="s">
+        <v>214</v>
+      </c>
+      <c r="C48" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E48" s="40" t="s">
+        <v>22</v>
+      </c>
+      <c r="F48" s="40" t="s">
+        <v>215</v>
+      </c>
+      <c r="G48" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="52" t="s">
+        <v>216</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="30" t="s">
+        <v>217</v>
+      </c>
+      <c r="B49" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="C49" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E49" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F49" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G49" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="37" t="s">
+        <v>219</v>
+      </c>
+      <c r="B50" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="C50" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E50" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F50" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="G50" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="52" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="30" t="s">
+        <v>221</v>
+      </c>
+      <c r="B51" s="31" t="s">
+        <v>222</v>
+      </c>
+      <c r="C51" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E51" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F51" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G51" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H51" s="36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="B52" s="38" t="s">
+        <v>224</v>
+      </c>
+      <c r="C52" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="40" t="s">
+        <v>32</v>
+      </c>
+      <c r="E52" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F52" s="40" t="s">
+        <v>203</v>
+      </c>
+      <c r="G52" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H52" s="52" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="30" t="s">
+        <v>225</v>
+      </c>
+      <c r="B53" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="C53" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="E53" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F53" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="G53" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="36" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="54" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A54" s="37" t="s">
+        <v>227</v>
+      </c>
+      <c r="B54" s="38" t="s">
+        <v>228</v>
+      </c>
+      <c r="C54" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="40" t="s">
+        <v>229</v>
+      </c>
+      <c r="E54" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F54" s="40" t="s">
+        <v>230</v>
+      </c>
+      <c r="G54" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="52" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="30" t="s">
+        <v>232</v>
+      </c>
+      <c r="B55" s="31" t="s">
+        <v>233</v>
+      </c>
+      <c r="C55" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E55" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F55" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="G55" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="37" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" s="38" t="s">
+        <v>237</v>
+      </c>
+      <c r="C56" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E56" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F56" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="G56" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" s="52" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="30" t="s">
+        <v>240</v>
+      </c>
+      <c r="B57" s="31" t="s">
+        <v>241</v>
+      </c>
+      <c r="C57" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E57" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F57" s="33" t="s">
+        <v>242</v>
+      </c>
+      <c r="G57" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H57" s="36" t="s">
+        <v>243</v>
+      </c>
+    </row>
+    <row r="58" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A58" s="37" t="s">
+        <v>244</v>
+      </c>
+      <c r="B58" s="38" t="s">
+        <v>245</v>
+      </c>
+      <c r="C58" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E58" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F58" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="G58" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="52" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="59" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A59" s="30" t="s">
+        <v>247</v>
+      </c>
+      <c r="B59" s="31" t="s">
+        <v>248</v>
+      </c>
+      <c r="C59" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E59" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F59" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="G59" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="36" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="60" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A60" s="37" t="s">
+        <v>250</v>
+      </c>
+      <c r="B60" s="38" t="s">
+        <v>251</v>
+      </c>
+      <c r="C60" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E60" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F60" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="G60" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="52" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="61" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A61" s="30" t="s">
+        <v>254</v>
+      </c>
+      <c r="B61" s="31" t="s">
+        <v>255</v>
+      </c>
+      <c r="C61" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E61" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F61" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="G61" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="36" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="62" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A62" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="B62" s="38" t="s">
+        <v>258</v>
+      </c>
+      <c r="C62" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E62" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F62" s="40" t="s">
+        <v>259</v>
+      </c>
+      <c r="G62" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="52" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="63" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A63" s="30" t="s">
+        <v>261</v>
+      </c>
+      <c r="B63" s="31" t="s">
+        <v>262</v>
+      </c>
+      <c r="C63" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E63" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F63" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="G63" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H63" s="36" t="s">
+        <v>263</v>
+      </c>
+    </row>
+    <row r="64" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A64" s="37" t="s">
+        <v>264</v>
+      </c>
+      <c r="B64" s="38" t="s">
+        <v>265</v>
+      </c>
+      <c r="C64" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E64" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F64" s="40" t="s">
+        <v>238</v>
+      </c>
+      <c r="G64" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="52" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A65" s="30" t="s">
+        <v>266</v>
+      </c>
+      <c r="B65" s="31" t="s">
+        <v>267</v>
+      </c>
+      <c r="C65" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E65" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F65" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="G65" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="36" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A66" s="37" t="s">
+        <v>270</v>
+      </c>
+      <c r="B66" s="38" t="s">
+        <v>271</v>
+      </c>
+      <c r="C66" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E66" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F66" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="G66" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H66" s="52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A67" s="30" t="s">
+        <v>272</v>
+      </c>
+      <c r="B67" s="31" t="s">
+        <v>273</v>
+      </c>
+      <c r="C67" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E67" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F67" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="G67" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="36" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="68" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A68" s="37" t="s">
+        <v>274</v>
+      </c>
+      <c r="B68" s="38" t="s">
+        <v>275</v>
+      </c>
+      <c r="C68" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E68" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F68" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="G68" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="52" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="69" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A69" s="30" t="s">
+        <v>277</v>
+      </c>
+      <c r="B69" s="31" t="s">
+        <v>278</v>
+      </c>
+      <c r="C69" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E69" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F69" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="G69" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="36" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="70" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A70" s="37" t="s">
+        <v>281</v>
+      </c>
+      <c r="B70" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="C70" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E70" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F70" s="40" t="s">
+        <v>283</v>
+      </c>
+      <c r="G70" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="52" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="71" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A71" s="30" t="s">
+        <v>285</v>
+      </c>
+      <c r="B71" s="31" t="s">
+        <v>286</v>
+      </c>
+      <c r="C71" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E71" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F71" s="33" t="s">
+        <v>287</v>
+      </c>
+      <c r="G71" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="36" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="72" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A72" s="37" t="s">
+        <v>289</v>
+      </c>
+      <c r="B72" s="38" t="s">
+        <v>290</v>
+      </c>
+      <c r="C72" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E72" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F72" s="40" t="s">
+        <v>242</v>
+      </c>
+      <c r="G72" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="52" t="s">
+        <v>291</v>
+      </c>
+    </row>
+    <row r="73" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A73" s="30" t="s">
+        <v>292</v>
+      </c>
+      <c r="B73" s="31" t="s">
+        <v>293</v>
+      </c>
+      <c r="C73" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E73" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F73" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="G73" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H73" s="36" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="74" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A74" s="37" t="s">
+        <v>295</v>
+      </c>
+      <c r="B74" s="38" t="s">
+        <v>296</v>
+      </c>
+      <c r="C74" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E74" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F74" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="G74" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H74" s="52" t="s">
+        <v>297</v>
+      </c>
+    </row>
+    <row r="75" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A75" s="30" t="s">
+        <v>298</v>
+      </c>
+      <c r="B75" s="31" t="s">
+        <v>299</v>
+      </c>
+      <c r="C75" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E75" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F75" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="G75" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H75" s="36" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="76" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A76" s="37" t="s">
+        <v>301</v>
+      </c>
+      <c r="B76" s="38" t="s">
+        <v>302</v>
+      </c>
+      <c r="C76" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E76" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F76" s="40" t="s">
+        <v>303</v>
+      </c>
+      <c r="G76" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H76" s="52" t="s">
+        <v>304</v>
+      </c>
+    </row>
+    <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A77" s="30" t="s">
+        <v>305</v>
+      </c>
+      <c r="B77" s="31" t="s">
+        <v>306</v>
+      </c>
+      <c r="C77" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E77" s="33" t="s">
+        <v>21</v>
+      </c>
+      <c r="F77" s="33" t="s">
+        <v>268</v>
+      </c>
+      <c r="G77" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H77" s="36" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A78" s="37" t="s">
+        <v>307</v>
+      </c>
+      <c r="B78" s="38" t="s">
+        <v>308</v>
+      </c>
+      <c r="C78" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E78" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F78" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="G78" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H78" s="52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="79" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A79" s="30" t="s">
+        <v>309</v>
+      </c>
+      <c r="B79" s="31" t="s">
+        <v>310</v>
+      </c>
+      <c r="C79" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E79" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F79" s="33" t="s">
+        <v>234</v>
+      </c>
+      <c r="G79" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H79" s="36" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A80" s="37" t="s">
+        <v>312</v>
+      </c>
+      <c r="B80" s="38" t="s">
+        <v>313</v>
+      </c>
+      <c r="C80" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E80" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F80" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="G80" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H80" s="52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="81" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A81" s="30" t="s">
+        <v>314</v>
+      </c>
+      <c r="B81" s="31" t="s">
+        <v>315</v>
+      </c>
+      <c r="C81" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E81" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F81" s="33" t="s">
+        <v>316</v>
+      </c>
+      <c r="G81" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H81" s="36" t="s">
+        <v>317</v>
+      </c>
+    </row>
+    <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A82" s="37" t="s">
+        <v>318</v>
+      </c>
+      <c r="B82" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="C82" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E82" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F82" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G82" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H82" s="52" t="s">
+        <v>320</v>
+      </c>
+    </row>
+    <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A83" s="30" t="s">
+        <v>321</v>
+      </c>
+      <c r="B83" s="31" t="s">
+        <v>322</v>
+      </c>
+      <c r="C83" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E83" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F83" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="G83" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H83" s="36" t="s">
+        <v>323</v>
+      </c>
+    </row>
+    <row r="84" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A84" s="37" t="s">
+        <v>324</v>
+      </c>
+      <c r="B84" s="38" t="s">
+        <v>325</v>
+      </c>
+      <c r="C84" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E84" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F84" s="40" t="s">
+        <v>252</v>
+      </c>
+      <c r="G84" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H84" s="52" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="85" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A85" s="30" t="s">
+        <v>327</v>
+      </c>
+      <c r="B85" s="31" t="s">
+        <v>328</v>
+      </c>
+      <c r="C85" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E85" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F85" s="33" t="s">
+        <v>252</v>
+      </c>
+      <c r="G85" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H85" s="36" t="s">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="37" t="s">
+        <v>329</v>
+      </c>
+      <c r="B86" s="38" t="s">
+        <v>330</v>
+      </c>
+      <c r="C86" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E86" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F86" s="40" t="s">
+        <v>331</v>
+      </c>
+      <c r="G86" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H86" s="52" t="s">
+        <v>332</v>
+      </c>
+    </row>
+    <row r="87" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="30" t="s">
+        <v>333</v>
+      </c>
+      <c r="B87" s="31" t="s">
+        <v>334</v>
+      </c>
+      <c r="C87" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E87" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F87" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="G87" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H87" s="36" t="s">
+        <v>335</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="37" t="s">
+        <v>336</v>
+      </c>
+      <c r="B88" s="38" t="s">
+        <v>337</v>
+      </c>
+      <c r="C88" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E88" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F88" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="G88" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H88" s="52" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="30" t="s">
+        <v>338</v>
+      </c>
+      <c r="B89" s="31" t="s">
+        <v>339</v>
+      </c>
+      <c r="C89" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" s="33" t="s">
+        <v>27</v>
+      </c>
+      <c r="F89" s="33" t="s">
+        <v>340</v>
+      </c>
+      <c r="G89" s="50" t="n">
+        <v>8</v>
+      </c>
+      <c r="H89" s="36" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="37" t="s">
+        <v>342</v>
+      </c>
+      <c r="B90" s="38" t="s">
+        <v>343</v>
+      </c>
+      <c r="C90" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E90" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F90" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="G90" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H90" s="52" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="30" t="s">
+        <v>346</v>
+      </c>
+      <c r="B91" s="31" t="s">
+        <v>347</v>
+      </c>
+      <c r="C91" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E91" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F91" s="33" t="s">
+        <v>348</v>
+      </c>
+      <c r="G91" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H91" s="36" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="37" t="s">
+        <v>350</v>
+      </c>
+      <c r="B92" s="38" t="s">
+        <v>351</v>
+      </c>
+      <c r="C92" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E92" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F92" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="G92" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H92" s="52" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="30" t="s">
+        <v>352</v>
+      </c>
+      <c r="B93" s="31" t="s">
+        <v>353</v>
+      </c>
+      <c r="C93" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E93" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F93" s="33" t="s">
+        <v>279</v>
+      </c>
+      <c r="G93" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H93" s="36" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="94" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A94" s="37" t="s">
+        <v>355</v>
+      </c>
+      <c r="B94" s="38" t="s">
+        <v>356</v>
+      </c>
+      <c r="C94" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E94" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F94" s="40" t="s">
+        <v>357</v>
+      </c>
+      <c r="G94" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H94" s="52" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="95" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A95" s="30" t="s">
+        <v>359</v>
+      </c>
+      <c r="B95" s="31" t="s">
+        <v>360</v>
+      </c>
+      <c r="C95" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E95" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F95" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="G95" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H95" s="36" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A96" s="37" t="s">
+        <v>362</v>
+      </c>
+      <c r="B96" s="38" t="s">
+        <v>363</v>
+      </c>
+      <c r="C96" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E96" s="40" t="s">
+        <v>21</v>
+      </c>
+      <c r="F96" s="40" t="s">
+        <v>268</v>
+      </c>
+      <c r="G96" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H96" s="52" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="97" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A97" s="30" t="s">
+        <v>365</v>
+      </c>
+      <c r="B97" s="31" t="s">
+        <v>366</v>
+      </c>
+      <c r="C97" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E97" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F97" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G97" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H97" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A98" s="37" t="s">
+        <v>367</v>
+      </c>
+      <c r="B98" s="38" t="s">
+        <v>368</v>
+      </c>
+      <c r="C98" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E98" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F98" s="40" t="s">
+        <v>137</v>
+      </c>
+      <c r="G98" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H98" s="52" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A99" s="30" t="s">
+        <v>369</v>
+      </c>
+      <c r="B99" s="31" t="s">
+        <v>370</v>
+      </c>
+      <c r="C99" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="33" t="s">
+        <v>69</v>
+      </c>
+      <c r="E99" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F99" s="33" t="s">
+        <v>344</v>
+      </c>
+      <c r="G99" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H99" s="36" t="s">
+        <v>371</v>
+      </c>
+    </row>
+    <row r="100" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A100" s="37" t="s">
+        <v>372</v>
+      </c>
+      <c r="B100" s="38" t="s">
+        <v>373</v>
+      </c>
+      <c r="C100" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E100" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F100" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="G100" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H100" s="52" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="101" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A101" s="30" t="s">
+        <v>374</v>
+      </c>
+      <c r="B101" s="31" t="s">
+        <v>375</v>
+      </c>
+      <c r="C101" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E101" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F101" s="33" t="s">
+        <v>376</v>
+      </c>
+      <c r="G101" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H101" s="36" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="102" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A102" s="37" t="s">
+        <v>378</v>
+      </c>
+      <c r="B102" s="38" t="s">
+        <v>379</v>
+      </c>
+      <c r="C102" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D102" s="40" t="s">
+        <v>69</v>
+      </c>
+      <c r="E102" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="F102" s="40" t="s">
+        <v>344</v>
+      </c>
+      <c r="G102" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H102" s="52" t="s">
+        <v>345</v>
+      </c>
+    </row>
+    <row r="103" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A103" s="30" t="s">
+        <v>380</v>
+      </c>
+      <c r="B103" s="31" t="s">
+        <v>381</v>
+      </c>
+      <c r="C103" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D103" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E103" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F103" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G103" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H103" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="104" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A104" s="37" t="s">
+        <v>382</v>
+      </c>
+      <c r="B104" s="38" t="s">
+        <v>383</v>
+      </c>
+      <c r="C104" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D104" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E104" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F104" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G104" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H104" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="105" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A105" s="30" t="s">
+        <v>384</v>
+      </c>
+      <c r="B105" s="31" t="s">
+        <v>385</v>
+      </c>
+      <c r="C105" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D105" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E105" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F105" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G105" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H105" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="106" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A106" s="37" t="s">
+        <v>386</v>
+      </c>
+      <c r="B106" s="38" t="s">
+        <v>387</v>
+      </c>
+      <c r="C106" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D106" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E106" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F106" s="40" t="s">
+        <v>388</v>
+      </c>
+      <c r="G106" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H106" s="52" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="107" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A107" s="30" t="s">
+        <v>390</v>
+      </c>
+      <c r="B107" s="31" t="s">
+        <v>391</v>
+      </c>
+      <c r="C107" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D107" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E107" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F107" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="G107" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H107" s="36" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="108" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A108" s="37" t="s">
+        <v>392</v>
+      </c>
+      <c r="B108" s="38" t="s">
+        <v>393</v>
+      </c>
+      <c r="C108" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D108" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E108" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F108" s="40" t="s">
+        <v>388</v>
+      </c>
+      <c r="G108" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H108" s="52" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="109" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A109" s="30" t="s">
+        <v>394</v>
+      </c>
+      <c r="B109" s="31" t="s">
+        <v>395</v>
+      </c>
+      <c r="C109" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D109" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E109" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F109" s="33" t="s">
+        <v>388</v>
+      </c>
+      <c r="G109" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H109" s="36" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="110" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A110" s="37" t="s">
+        <v>396</v>
+      </c>
+      <c r="B110" s="38" t="s">
+        <v>397</v>
+      </c>
+      <c r="C110" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D110" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E110" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F110" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G110" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H110" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="111" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A111" s="30" t="s">
+        <v>398</v>
+      </c>
+      <c r="B111" s="31" t="s">
+        <v>399</v>
+      </c>
+      <c r="C111" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D111" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E111" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F111" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G111" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H111" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="112" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A112" s="37" t="s">
+        <v>400</v>
+      </c>
+      <c r="B112" s="38" t="s">
+        <v>401</v>
+      </c>
+      <c r="C112" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D112" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E112" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F112" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G112" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H112" s="52" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="113" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A113" s="30" t="s">
+        <v>402</v>
+      </c>
+      <c r="B113" s="31" t="s">
+        <v>403</v>
+      </c>
+      <c r="C113" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D113" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E113" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F113" s="33" t="s">
+        <v>97</v>
+      </c>
+      <c r="G113" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H113" s="36" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A114" s="37" t="s">
+        <v>404</v>
+      </c>
+      <c r="B114" s="38" t="s">
+        <v>405</v>
+      </c>
+      <c r="C114" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D114" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E114" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="F114" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G114" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H114" s="52" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="115" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A115" s="30" t="s">
+        <v>407</v>
+      </c>
+      <c r="B115" s="31" t="s">
+        <v>408</v>
+      </c>
+      <c r="C115" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D115" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F115" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G115" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H115" s="36" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A116" s="37" t="s">
+        <v>409</v>
+      </c>
+      <c r="B116" s="38" t="s">
+        <v>319</v>
+      </c>
+      <c r="C116" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D116" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E116" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="F116" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G116" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H116" s="52" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="117" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A117" s="30" t="s">
+        <v>410</v>
+      </c>
+      <c r="B117" s="31" t="s">
+        <v>411</v>
+      </c>
+      <c r="C117" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D117" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E117" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F117" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G117" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H117" s="36" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A118" s="37" t="s">
+        <v>413</v>
+      </c>
+      <c r="B118" s="38" t="s">
+        <v>414</v>
+      </c>
+      <c r="C118" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D118" s="40" t="s">
+        <v>82</v>
+      </c>
+      <c r="E118" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F118" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G118" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H118" s="52" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A119" s="30" t="s">
+        <v>416</v>
+      </c>
+      <c r="B119" s="31" t="s">
+        <v>417</v>
+      </c>
+      <c r="C119" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D119" s="33" t="s">
+        <v>82</v>
+      </c>
+      <c r="E119" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F119" s="33" t="s">
+        <v>143</v>
+      </c>
+      <c r="G119" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H119" s="36" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="120" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A120" s="37" t="s">
+        <v>419</v>
+      </c>
+      <c r="B120" s="38" t="s">
+        <v>420</v>
+      </c>
+      <c r="C120" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D120" s="40" t="s">
+        <v>64</v>
+      </c>
+      <c r="E120" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F120" s="40" t="s">
+        <v>78</v>
+      </c>
+      <c r="G120" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H120" s="52" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A121" s="30" t="s">
+        <v>422</v>
+      </c>
+      <c r="B121" s="31" t="s">
+        <v>423</v>
+      </c>
+      <c r="C121" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D121" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E121" s="33" t="s">
+        <v>18</v>
+      </c>
+      <c r="F121" s="33" t="s">
+        <v>424</v>
+      </c>
+      <c r="G121" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H121" s="36" t="s">
+        <v>425</v>
+      </c>
+    </row>
+    <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A122" s="37" t="s">
+        <v>426</v>
+      </c>
+      <c r="B122" s="38" t="s">
+        <v>427</v>
+      </c>
+      <c r="C122" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D122" s="40" t="s">
+        <v>26</v>
+      </c>
+      <c r="E122" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F122" s="40" t="s">
+        <v>123</v>
+      </c>
+      <c r="G122" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H122" s="52" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="123" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A123" s="30" t="s">
+        <v>429</v>
+      </c>
+      <c r="B123" s="31" t="s">
+        <v>430</v>
+      </c>
+      <c r="C123" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D123" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F123" s="33" t="s">
+        <v>83</v>
+      </c>
+      <c r="G123" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H123" s="36" t="s">
+        <v>431</v>
+      </c>
+    </row>
+    <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A124" s="37" t="s">
+        <v>432</v>
+      </c>
+      <c r="B124" s="38" t="s">
+        <v>433</v>
+      </c>
+      <c r="C124" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D124" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F124" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G124" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H124" s="52" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="125" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A125" s="30" t="s">
+        <v>435</v>
+      </c>
+      <c r="B125" s="31" t="s">
+        <v>436</v>
+      </c>
+      <c r="C125" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D125" s="33" t="s">
+        <v>24</v>
+      </c>
+      <c r="E125" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F125" s="33" t="s">
+        <v>437</v>
+      </c>
+      <c r="G125" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H125" s="36" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A126" s="37" t="s">
+        <v>439</v>
+      </c>
+      <c r="B126" s="38" t="s">
+        <v>440</v>
+      </c>
+      <c r="C126" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D126" s="40" t="s">
+        <v>24</v>
+      </c>
+      <c r="E126" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F126" s="40" t="s">
+        <v>83</v>
+      </c>
+      <c r="G126" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H126" s="52" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A127" s="30" t="s">
+        <v>441</v>
+      </c>
+      <c r="B127" s="31" t="s">
+        <v>442</v>
+      </c>
+      <c r="C127" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D127" s="33" t="s">
+        <v>19</v>
+      </c>
+      <c r="E127" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F127" s="33" t="s">
+        <v>443</v>
+      </c>
+      <c r="G127" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H127" s="36" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A128" s="37" t="s">
+        <v>445</v>
+      </c>
+      <c r="B128" s="38" t="s">
+        <v>446</v>
+      </c>
+      <c r="C128" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D128" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="E128" s="40" t="s">
+        <v>31</v>
+      </c>
+      <c r="F128" s="40" t="s">
+        <v>447</v>
+      </c>
+      <c r="G128" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H128" s="52" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A129" s="30" t="s">
+        <v>449</v>
+      </c>
+      <c r="B129" s="31" t="s">
+        <v>450</v>
+      </c>
+      <c r="C129" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D129" s="33" t="s">
+        <v>64</v>
+      </c>
+      <c r="E129" s="33" t="s">
+        <v>32</v>
+      </c>
+      <c r="F129" s="33" t="s">
+        <v>451</v>
+      </c>
+      <c r="G129" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H129" s="36" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A130" s="37" t="s">
+        <v>453</v>
+      </c>
+      <c r="B130" s="38" t="s">
+        <v>454</v>
+      </c>
+      <c r="C130" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D130" s="40" t="s">
+        <v>18</v>
+      </c>
+      <c r="E130" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F130" s="40" t="s">
+        <v>455</v>
+      </c>
+      <c r="G130" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H130" s="52" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A131" s="30" t="s">
+        <v>457</v>
+      </c>
+      <c r="B131" s="31" t="s">
+        <v>458</v>
+      </c>
+      <c r="C131" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D131" s="33" t="s">
+        <v>31</v>
+      </c>
+      <c r="E131" s="33" t="s">
+        <v>28</v>
+      </c>
+      <c r="F131" s="33" t="s">
+        <v>447</v>
+      </c>
+      <c r="G131" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H131" s="36" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="132" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A132" s="37" t="s">
+        <v>459</v>
+      </c>
+      <c r="B132" s="38" t="s">
+        <v>460</v>
+      </c>
+      <c r="C132" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D132" s="40" t="s">
+        <v>30</v>
+      </c>
+      <c r="E132" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F132" s="40" t="s">
+        <v>129</v>
+      </c>
+      <c r="G132" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H132" s="52" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A133" s="30" t="s">
+        <v>461</v>
+      </c>
+      <c r="B133" s="31" t="s">
+        <v>462</v>
+      </c>
+      <c r="C133" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D133" s="33" t="s">
+        <v>30</v>
+      </c>
+      <c r="E133" s="49" t="s">
+        <v>33</v>
+      </c>
+      <c r="F133" s="33" t="s">
+        <v>129</v>
+      </c>
+      <c r="G133" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H133" s="36" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A134" s="43" t="s">
         <v>59</v>
       </c>
-      <c r="B7" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D7" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="G7" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="43" t="s">
-        <v>63</v>
-      </c>
-      <c r="B8" s="44" t="s">
-        <v>64</v>
-      </c>
-      <c r="C8" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D8" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E8" s="45" t="s">
-        <v>19</v>
-      </c>
-      <c r="F8" s="45" t="s">
-        <v>65</v>
-      </c>
-      <c r="G8" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H8" s="47" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="B9" s="29" t="s">
-        <v>68</v>
-      </c>
-      <c r="C9" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D9" s="31" t="s">
-        <v>51</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>20</v>
-      </c>
-      <c r="F9" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="G9" s="42" t="n">
-        <v>21</v>
-      </c>
-      <c r="H9" s="34" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="43" t="s">
-        <v>71</v>
-      </c>
-      <c r="B10" s="44" t="s">
-        <v>72</v>
-      </c>
-      <c r="C10" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D10" s="45" t="s">
-        <v>51</v>
-      </c>
-      <c r="E10" s="45" t="s">
-        <v>21</v>
-      </c>
-      <c r="F10" s="45" t="s">
-        <v>69</v>
-      </c>
-      <c r="G10" s="48" t="n">
-        <v>5</v>
-      </c>
-      <c r="H10" s="47" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="B11" s="29" t="s">
-        <v>75</v>
-      </c>
-      <c r="C11" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="E11" s="31" t="s">
-        <v>23</v>
-      </c>
-      <c r="F11" s="31" t="s">
-        <v>76</v>
-      </c>
-      <c r="G11" s="42" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" s="34" t="s">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="43" t="s">
-        <v>78</v>
-      </c>
-      <c r="B12" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C12" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D12" s="45" t="s">
-        <v>80</v>
-      </c>
-      <c r="E12" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="F12" s="45" t="s">
-        <v>81</v>
-      </c>
-      <c r="G12" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="47" t="s">
-        <v>82</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="B13" s="29" t="s">
-        <v>84</v>
-      </c>
-      <c r="C13" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D13" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="F13" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="G13" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H13" s="34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="43" t="s">
-        <v>87</v>
-      </c>
-      <c r="B14" s="44" t="s">
-        <v>88</v>
-      </c>
-      <c r="C14" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D14" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="F14" s="45" t="s">
-        <v>89</v>
-      </c>
-      <c r="G14" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H14" s="47" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="15" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="28" t="s">
-        <v>91</v>
-      </c>
-      <c r="B15" s="29" t="s">
-        <v>92</v>
-      </c>
-      <c r="C15" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D15" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>22</v>
-      </c>
-      <c r="F15" s="31" t="s">
-        <v>85</v>
-      </c>
-      <c r="G15" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H15" s="34" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="43" t="s">
-        <v>93</v>
-      </c>
-      <c r="B16" s="44" t="s">
-        <v>94</v>
-      </c>
-      <c r="C16" s="40" t="s">
-        <v>3</v>
-      </c>
-      <c r="D16" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="45" t="s">
-        <v>22</v>
-      </c>
-      <c r="F16" s="45" t="s">
-        <v>95</v>
-      </c>
-      <c r="G16" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H16" s="47" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="28" t="s">
-        <v>97</v>
-      </c>
-      <c r="B17" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="C17" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D17" s="31" t="s">
-        <v>99</v>
-      </c>
-      <c r="E17" s="31" t="s">
-        <v>15</v>
-      </c>
-      <c r="F17" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="G17" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" s="34" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="43" t="s">
-        <v>102</v>
-      </c>
-      <c r="B18" s="44" t="s">
-        <v>103</v>
-      </c>
-      <c r="C18" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D18" s="45" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="49" t="s">
-        <v>24</v>
-      </c>
-      <c r="F18" s="45" t="s">
-        <v>104</v>
-      </c>
-      <c r="G18" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H18" s="47" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="B19" s="29" t="s">
-        <v>107</v>
-      </c>
-      <c r="C19" s="30" t="s">
-        <v>4</v>
-      </c>
-      <c r="D19" s="31" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="F19" s="31" t="s">
-        <v>104</v>
-      </c>
-      <c r="G19" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H19" s="34" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B20" s="36"/>
-      <c r="C20" s="36"/>
-      <c r="D20" s="36"/>
-      <c r="E20" s="36"/>
-      <c r="F20" s="36"/>
-      <c r="G20" s="37" t="n">
-        <f aca="false">SUM(G5:G19)</f>
-        <v>40</v>
-      </c>
-      <c r="H20" s="36"/>
+      <c r="B134" s="44"/>
+      <c r="C134" s="44"/>
+      <c r="D134" s="44"/>
+      <c r="E134" s="44"/>
+      <c r="F134" s="44"/>
+      <c r="G134" s="45" t="n">
+        <f aca="false">SUM(G5:G133)</f>
+        <v>48</v>
+      </c>
+      <c r="H134" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H19"/>
+  <autoFilter ref="A4:H133"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -2680,17 +6947,131 @@
     <hyperlink ref="A6" r:id="rId2" display="MEG-19584"/>
     <hyperlink ref="A7" r:id="rId3" display="MEG-19591"/>
     <hyperlink ref="A8" r:id="rId4" display="MEG-19723"/>
-    <hyperlink ref="A9" r:id="rId5" display="MEG-20107"/>
-    <hyperlink ref="A10" r:id="rId6" display="MEG-20258"/>
-    <hyperlink ref="A11" r:id="rId7" display="MEG-20651"/>
-    <hyperlink ref="A12" r:id="rId8" display="STAR-1688"/>
-    <hyperlink ref="A13" r:id="rId9" display="STAR-1692"/>
-    <hyperlink ref="A14" r:id="rId10" display="STAR-1693"/>
-    <hyperlink ref="A15" r:id="rId11" display="STAR-1694"/>
-    <hyperlink ref="A16" r:id="rId12" display="STAR-1695"/>
-    <hyperlink ref="A17" r:id="rId13" display="IP-1793"/>
-    <hyperlink ref="A18" r:id="rId14" display="MEG-19721"/>
-    <hyperlink ref="A19" r:id="rId15" display="MEG-19724"/>
+    <hyperlink ref="A9" r:id="rId5" display="MEG-19851"/>
+    <hyperlink ref="A10" r:id="rId6" display="MEG-19852"/>
+    <hyperlink ref="A11" r:id="rId7" display="MEG-19853"/>
+    <hyperlink ref="A12" r:id="rId8" display="MEG-19938"/>
+    <hyperlink ref="A13" r:id="rId9" display="MEG-20014"/>
+    <hyperlink ref="A14" r:id="rId10" display="MEG-20019"/>
+    <hyperlink ref="A15" r:id="rId11" display="MEG-20027"/>
+    <hyperlink ref="A16" r:id="rId12" display="MEG-20107"/>
+    <hyperlink ref="A17" r:id="rId13" display="MEG-20258"/>
+    <hyperlink ref="A18" r:id="rId14" display="MEG-20651"/>
+    <hyperlink ref="A19" r:id="rId15" display="STAR-1688"/>
+    <hyperlink ref="A20" r:id="rId16" display="STAR-1692"/>
+    <hyperlink ref="A21" r:id="rId17" display="STAR-1693"/>
+    <hyperlink ref="A22" r:id="rId18" display="STAR-1694"/>
+    <hyperlink ref="A23" r:id="rId19" display="STAR-1695"/>
+    <hyperlink ref="A24" r:id="rId20" display="IP-1793"/>
+    <hyperlink ref="A25" r:id="rId21" display="MEG-19721"/>
+    <hyperlink ref="A26" r:id="rId22" display="MEG-19724"/>
+    <hyperlink ref="A27" r:id="rId23" display="MEG-20025"/>
+    <hyperlink ref="A28" r:id="rId24" display="MEG-20026"/>
+    <hyperlink ref="A29" r:id="rId25" display="CR-1027"/>
+    <hyperlink ref="A30" r:id="rId26" display="CR-1045"/>
+    <hyperlink ref="A31" r:id="rId27" display="CR-1155"/>
+    <hyperlink ref="A32" r:id="rId28" display="CR-1263"/>
+    <hyperlink ref="A33" r:id="rId29" display="CR-1268"/>
+    <hyperlink ref="A34" r:id="rId30" display="CR-1284"/>
+    <hyperlink ref="A35" r:id="rId31" display="CR-1285"/>
+    <hyperlink ref="A36" r:id="rId32" display="CR-1316"/>
+    <hyperlink ref="A37" r:id="rId33" display="CR-1338"/>
+    <hyperlink ref="A38" r:id="rId34" display="CR-1381"/>
+    <hyperlink ref="A39" r:id="rId35" display="CR-1421"/>
+    <hyperlink ref="A40" r:id="rId36" display="CR-859"/>
+    <hyperlink ref="A41" r:id="rId37" display="IP-2525"/>
+    <hyperlink ref="A42" r:id="rId38" display="IP-2879"/>
+    <hyperlink ref="A43" r:id="rId39" display="IP-3022"/>
+    <hyperlink ref="A44" r:id="rId40" display="IP-3170"/>
+    <hyperlink ref="A45" r:id="rId41" display="IR-447"/>
+    <hyperlink ref="A46" r:id="rId42" display="IR-450"/>
+    <hyperlink ref="A47" r:id="rId43" display="IR-461"/>
+    <hyperlink ref="A48" r:id="rId44" display="IR-481"/>
+    <hyperlink ref="A49" r:id="rId45" display="IR-493"/>
+    <hyperlink ref="A50" r:id="rId46" display="IR-494"/>
+    <hyperlink ref="A51" r:id="rId47" display="IR-495"/>
+    <hyperlink ref="A52" r:id="rId48" display="IR-496"/>
+    <hyperlink ref="A53" r:id="rId49" display="IR-497"/>
+    <hyperlink ref="A54" r:id="rId50" display="IR-812"/>
+    <hyperlink ref="A55" r:id="rId51" display="MEG-18880"/>
+    <hyperlink ref="A56" r:id="rId52" display="MEG-18920"/>
+    <hyperlink ref="A57" r:id="rId53" display="MEG-18923"/>
+    <hyperlink ref="A58" r:id="rId54" display="MEG-18924"/>
+    <hyperlink ref="A59" r:id="rId55" display="MEG-18925"/>
+    <hyperlink ref="A60" r:id="rId56" display="MEG-18926"/>
+    <hyperlink ref="A61" r:id="rId57" display="MEG-18927"/>
+    <hyperlink ref="A62" r:id="rId58" display="MEG-18928"/>
+    <hyperlink ref="A63" r:id="rId59" display="MEG-18929"/>
+    <hyperlink ref="A64" r:id="rId60" display="MEG-18931"/>
+    <hyperlink ref="A65" r:id="rId61" display="MEG-18932"/>
+    <hyperlink ref="A66" r:id="rId62" display="MEG-18933"/>
+    <hyperlink ref="A67" r:id="rId63" display="MEG-18934"/>
+    <hyperlink ref="A68" r:id="rId64" display="MEG-18937"/>
+    <hyperlink ref="A69" r:id="rId65" display="MEG-18938"/>
+    <hyperlink ref="A70" r:id="rId66" display="MEG-18939"/>
+    <hyperlink ref="A71" r:id="rId67" display="MEG-18941"/>
+    <hyperlink ref="A72" r:id="rId68" display="MEG-18942"/>
+    <hyperlink ref="A73" r:id="rId69" display="MEG-18943"/>
+    <hyperlink ref="A74" r:id="rId70" display="MEG-18945"/>
+    <hyperlink ref="A75" r:id="rId71" display="MEG-18947"/>
+    <hyperlink ref="A76" r:id="rId72" display="MEG-18948"/>
+    <hyperlink ref="A77" r:id="rId73" display="MEG-18955"/>
+    <hyperlink ref="A78" r:id="rId74" display="MEG-18956"/>
+    <hyperlink ref="A79" r:id="rId75" display="MEG-19147"/>
+    <hyperlink ref="A80" r:id="rId76" display="MEG-19158"/>
+    <hyperlink ref="A81" r:id="rId77" display="MEG-19192"/>
+    <hyperlink ref="A82" r:id="rId78" display="MEG-19200"/>
+    <hyperlink ref="A83" r:id="rId79" display="MEG-19224"/>
+    <hyperlink ref="A84" r:id="rId80" display="MEG-19225"/>
+    <hyperlink ref="A85" r:id="rId81" display="MEG-19226"/>
+    <hyperlink ref="A86" r:id="rId82" display="MEG-19263"/>
+    <hyperlink ref="A87" r:id="rId83" display="MEG-19299"/>
+    <hyperlink ref="A88" r:id="rId84" display="MEG-19365"/>
+    <hyperlink ref="A89" r:id="rId85" display="MEG-19374"/>
+    <hyperlink ref="A90" r:id="rId86" display="MEG-19418"/>
+    <hyperlink ref="A91" r:id="rId87" display="MEG-19440"/>
+    <hyperlink ref="A92" r:id="rId88" display="MEG-19585"/>
+    <hyperlink ref="A93" r:id="rId89" display="MEG-19598"/>
+    <hyperlink ref="A94" r:id="rId90" display="MEG-19699"/>
+    <hyperlink ref="A95" r:id="rId91" display="MEG-19718"/>
+    <hyperlink ref="A96" r:id="rId92" display="MEG-19856"/>
+    <hyperlink ref="A97" r:id="rId93" display="MEG-19857"/>
+    <hyperlink ref="A98" r:id="rId94" display="MEG-19944"/>
+    <hyperlink ref="A99" r:id="rId95" display="MEG-19964"/>
+    <hyperlink ref="A100" r:id="rId96" display="MEG-19970"/>
+    <hyperlink ref="A101" r:id="rId97" display="MEG-20087"/>
+    <hyperlink ref="A102" r:id="rId98" display="MEG-20143"/>
+    <hyperlink ref="A103" r:id="rId99" display="MEG-20230"/>
+    <hyperlink ref="A104" r:id="rId100" display="MEG-20231"/>
+    <hyperlink ref="A105" r:id="rId101" display="MEG-20232"/>
+    <hyperlink ref="A106" r:id="rId102" display="MEG-20233"/>
+    <hyperlink ref="A107" r:id="rId103" display="MEG-20234"/>
+    <hyperlink ref="A108" r:id="rId104" display="MEG-20235"/>
+    <hyperlink ref="A109" r:id="rId105" display="MEG-20236"/>
+    <hyperlink ref="A110" r:id="rId106" display="MEG-20237"/>
+    <hyperlink ref="A111" r:id="rId107" display="MEG-20238"/>
+    <hyperlink ref="A112" r:id="rId108" display="MEG-20239"/>
+    <hyperlink ref="A113" r:id="rId109" display="MEG-20240"/>
+    <hyperlink ref="A114" r:id="rId110" display="MEG-20294"/>
+    <hyperlink ref="A115" r:id="rId111" display="MEG-20318"/>
+    <hyperlink ref="A116" r:id="rId112" display="MEG-20724"/>
+    <hyperlink ref="A117" r:id="rId113" display="MEG-20726"/>
+    <hyperlink ref="A118" r:id="rId114" display="MEG-20812"/>
+    <hyperlink ref="A119" r:id="rId115" display="MEG-20813"/>
+    <hyperlink ref="A120" r:id="rId116" display="MEG-20945"/>
+    <hyperlink ref="A121" r:id="rId117" display="MEG-21328"/>
+    <hyperlink ref="A122" r:id="rId118" display="MEG-21782"/>
+    <hyperlink ref="A123" r:id="rId119" display="MEG-21937"/>
+    <hyperlink ref="A124" r:id="rId120" display="MEG-21938"/>
+    <hyperlink ref="A125" r:id="rId121" display="MEG-21939"/>
+    <hyperlink ref="A126" r:id="rId122" display="MEG-21979"/>
+    <hyperlink ref="A127" r:id="rId123" display="MEG-22118"/>
+    <hyperlink ref="A128" r:id="rId124" display="MEG-22141"/>
+    <hyperlink ref="A129" r:id="rId125" display="MEG-22234"/>
+    <hyperlink ref="A130" r:id="rId126" display="MEG-22495"/>
+    <hyperlink ref="A131" r:id="rId127" display="MEG-22540"/>
+    <hyperlink ref="A132" r:id="rId128" display="STAR-1689"/>
+    <hyperlink ref="A133" r:id="rId129" display="STAR-1696"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2699,7 +7080,7 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId16"/>
+  <drawing r:id="rId130"/>
 </worksheet>
 </file>
 
@@ -2709,7 +7090,7 @@
     <tabColor rgb="FF64748B"/>
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H8"/>
+  <dimension ref="A1:H9"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="13"/>
@@ -2721,150 +7102,176 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="50" t="s">
-        <v>108</v>
-      </c>
-      <c r="B1" s="50"/>
-      <c r="C1" s="50"/>
-      <c r="D1" s="50"/>
-      <c r="E1" s="50"/>
-      <c r="F1" s="50"/>
-      <c r="G1" s="50"/>
-      <c r="H1" s="50"/>
+      <c r="A1" s="54" t="s">
+        <v>464</v>
+      </c>
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="54"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="54"/>
+      <c r="H1" s="54"/>
     </row>
     <row r="2" customFormat="false" ht="18" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="51" t="s">
-        <v>109</v>
-      </c>
-      <c r="B2" s="51"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="51"/>
-      <c r="E2" s="51"/>
-      <c r="F2" s="51"/>
-      <c r="G2" s="51"/>
-      <c r="H2" s="51"/>
+      <c r="A2" s="55" t="s">
+        <v>465</v>
+      </c>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
+      <c r="D2" s="55"/>
+      <c r="E2" s="55"/>
+      <c r="F2" s="55"/>
+      <c r="G2" s="55"/>
+      <c r="H2" s="55"/>
     </row>
     <row r="4" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="26" t="s">
-        <v>36</v>
-      </c>
-      <c r="B4" s="27" t="s">
-        <v>37</v>
-      </c>
-      <c r="C4" s="27" t="s">
-        <v>7</v>
-      </c>
-      <c r="D4" s="27" t="s">
-        <v>38</v>
-      </c>
-      <c r="E4" s="27" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" s="27" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" s="27" t="s">
-        <v>41</v>
+      <c r="A4" s="28" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4" s="29" t="s">
+        <v>46</v>
+      </c>
+      <c r="C4" s="29" t="s">
+        <v>8</v>
+      </c>
+      <c r="D4" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4" s="29" t="s">
+        <v>11</v>
+      </c>
+      <c r="F4" s="29" t="s">
+        <v>48</v>
+      </c>
+      <c r="G4" s="29" t="s">
+        <v>49</v>
+      </c>
+      <c r="H4" s="29" t="s">
+        <v>50</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="28" t="s">
-        <v>110</v>
-      </c>
-      <c r="B5" s="29" t="s">
-        <v>111</v>
-      </c>
-      <c r="C5" s="40" t="s">
+      <c r="A5" s="30" t="s">
+        <v>466</v>
+      </c>
+      <c r="B5" s="31" t="s">
+        <v>467</v>
+      </c>
+      <c r="C5" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D5" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E5" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="F5" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="G5" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" s="34" t="s">
-        <v>113</v>
+      <c r="D5" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="E5" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="F5" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="36" t="s">
+        <v>469</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="C6" s="40" t="s">
+      <c r="A6" s="37" t="s">
+        <v>470</v>
+      </c>
+      <c r="B6" s="38" t="s">
+        <v>471</v>
+      </c>
+      <c r="C6" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D6" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="E6" s="45" t="s">
-        <v>112</v>
-      </c>
-      <c r="F6" s="45" t="s">
-        <v>44</v>
-      </c>
-      <c r="G6" s="46" t="n">
-        <v>0</v>
-      </c>
-      <c r="H6" s="47" t="s">
-        <v>116</v>
+      <c r="D6" s="40" t="s">
+        <v>468</v>
+      </c>
+      <c r="E6" s="40" t="s">
+        <v>468</v>
+      </c>
+      <c r="F6" s="40" t="s">
+        <v>53</v>
+      </c>
+      <c r="G6" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="52" t="s">
+        <v>472</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="28" t="s">
-        <v>117</v>
-      </c>
-      <c r="B7" s="29" t="s">
-        <v>118</v>
-      </c>
-      <c r="C7" s="40" t="s">
+      <c r="A7" s="30" t="s">
+        <v>473</v>
+      </c>
+      <c r="B7" s="31" t="s">
+        <v>474</v>
+      </c>
+      <c r="C7" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="D7" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="E7" s="31" t="s">
-        <v>112</v>
-      </c>
-      <c r="F7" s="31" t="s">
-        <v>44</v>
-      </c>
-      <c r="G7" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="H7" s="34" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="35" t="s">
-        <v>46</v>
-      </c>
-      <c r="B8" s="36"/>
-      <c r="C8" s="36"/>
-      <c r="D8" s="36"/>
-      <c r="E8" s="36"/>
-      <c r="F8" s="36"/>
-      <c r="G8" s="37" t="n">
-        <f aca="false">SUM(G5:G7)</f>
-        <v>0</v>
-      </c>
-      <c r="H8" s="36"/>
+      <c r="D7" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="E7" s="33" t="s">
+        <v>468</v>
+      </c>
+      <c r="F7" s="33" t="s">
+        <v>53</v>
+      </c>
+      <c r="G7" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="36" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="23.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="37" t="s">
+        <v>476</v>
+      </c>
+      <c r="B8" s="38" t="s">
+        <v>477</v>
+      </c>
+      <c r="C8" s="39" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="40" t="s">
+        <v>57</v>
+      </c>
+      <c r="E8" s="53" t="s">
+        <v>33</v>
+      </c>
+      <c r="F8" s="40" t="s">
+        <v>478</v>
+      </c>
+      <c r="G8" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="52" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="43" t="s">
+        <v>59</v>
+      </c>
+      <c r="B9" s="44"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="44"/>
+      <c r="E9" s="44"/>
+      <c r="F9" s="44"/>
+      <c r="G9" s="45" t="n">
+        <f aca="false">SUM(G5:G8)</f>
+        <v>0</v>
+      </c>
+      <c r="H9" s="44"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:H7"/>
+  <autoFilter ref="A4:H8"/>
   <mergeCells count="2">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
@@ -2873,6 +7280,7 @@
     <hyperlink ref="A5" r:id="rId1" display="CBT-137"/>
     <hyperlink ref="A6" r:id="rId2" display="CBT-85"/>
     <hyperlink ref="A7" r:id="rId3" display="CBT-97"/>
+    <hyperlink ref="A8" r:id="rId4" display="IR-907"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2881,6 +7289,6 @@
     <oddHeader/>
     <oddFooter/>
   </headerFooter>
-  <drawing r:id="rId4"/>
+  <drawing r:id="rId5"/>
 </worksheet>
 </file>